--- a/SGC-CKN/Excel/607e0e0c-05b6-4e68-a67b-e50624c0c032_LÔ_CT-02_P7-132_D800_18-03-2026.xlsx
+++ b/SGC-CKN/Excel/607e0e0c-05b6-4e68-a67b-e50624c0c032_LÔ_CT-02_P7-132_D800_18-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
   <si>
     <t>Dự án</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>18:10 18/03/2026</t>
+    <t>17:10 18/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -102,7 +102,7 @@
 18/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">09:20
+    <t xml:space="preserve">08:20
 18/03/2026</t>
   </si>
   <si>
@@ -115,20 +115,24 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">09:21
+    <t xml:space="preserve">08:21
 18/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:40
+18/03/2026</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">09:40
 18/03/2026</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">10:30
 18/03/2026</t>
   </si>
@@ -224,7 +228,7 @@
 18/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">18:10
+    <t xml:space="preserve">17:10
 18/03/2026</t>
   </si>
   <si>
@@ -262,7 +266,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -318,12 +322,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF365314"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -361,7 +359,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -415,7 +413,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -426,11 +424,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -541,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -603,29 +596,35 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -645,22 +644,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1252,13 +1242,13 @@
         <v>7.53</v>
       </c>
       <c r="H11" s="5">
-        <v>1.33</v>
+        <v>0.33</v>
       </c>
       <c r="I11" s="5">
         <v>7.53</v>
       </c>
       <c r="J11" s="8">
-        <v>5.65</v>
+        <v>22.59</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1310,25 +1300,25 @@
         <v>36</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="12">
         <v>9.42</v>
       </c>
       <c r="G13" s="12">
-        <v>18.42</v>
+        <v>17.42</v>
       </c>
       <c r="H13" s="12">
         <v>0.83</v>
       </c>
       <c r="I13" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" s="8">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1336,34 +1326,34 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="15">
-        <v>18.42</v>
+        <v>17.42</v>
       </c>
       <c r="G14" s="15">
-        <v>24.32</v>
+        <v>21.32</v>
       </c>
       <c r="H14" s="15">
         <v>0.57</v>
       </c>
       <c r="I14" s="15">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="J14" s="8">
-        <v>10.41</v>
+        <v>6.88</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
@@ -1371,34 +1361,34 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" s="18">
-        <v>24.32</v>
+        <v>21.32</v>
       </c>
       <c r="G15" s="18">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="H15" s="18">
         <v>0.9</v>
       </c>
       <c r="I15" s="18">
-        <v>0.78</v>
+        <v>4.08</v>
       </c>
       <c r="J15" s="21">
-        <v>0.87</v>
+        <v>4.53</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1406,22 +1396,22 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" s="22">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="G16" s="22">
         <v>35.8</v>
@@ -1430,10 +1420,10 @@
         <v>0.67</v>
       </c>
       <c r="I16" s="22">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="J16" s="8">
-        <v>16.05</v>
+        <v>15.6</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1441,158 +1431,158 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F17" s="25">
         <v>35.8</v>
       </c>
       <c r="G17" s="25">
-        <v>38.34</v>
+        <v>37.84</v>
       </c>
       <c r="H17" s="25">
         <v>1.15</v>
       </c>
       <c r="I17" s="25">
-        <v>2.54</v>
-      </c>
-      <c r="J17" s="28">
-        <v>2.21</v>
+        <v>2.04</v>
+      </c>
+      <c r="J17" s="21">
+        <v>1.77</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="29" t="s">
+      <c r="A18" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="31" t="s">
+      <c r="C18" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="29">
-        <v>38.34</v>
-      </c>
-      <c r="G18" s="29">
+      <c r="E18" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="28">
+        <v>37.84</v>
+      </c>
+      <c r="G18" s="28">
         <v>39.6</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>0.48</v>
       </c>
-      <c r="I18" s="29">
-        <v>1.26</v>
-      </c>
-      <c r="J18" s="28">
-        <v>2.61</v>
-      </c>
-      <c r="K18" s="30" t="s">
+      <c r="I18" s="28">
+        <v>1.76</v>
+      </c>
+      <c r="J18" s="21">
+        <v>3.64</v>
+      </c>
+      <c r="K18" s="29" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="32" t="s">
+      <c r="A19" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="34" t="s">
+      <c r="C19" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="D19" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="32">
+      <c r="E19" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="31">
         <v>39.6</v>
       </c>
-      <c r="G19" s="32">
-        <v>44.07</v>
-      </c>
-      <c r="H19" s="32">
+      <c r="G19" s="31">
+        <v>44.02</v>
+      </c>
+      <c r="H19" s="31">
         <v>1.32</v>
       </c>
-      <c r="I19" s="32">
-        <v>4.47</v>
-      </c>
-      <c r="J19" s="28">
-        <v>3.39</v>
-      </c>
-      <c r="K19" s="33" t="s">
+      <c r="I19" s="31">
+        <v>4.42</v>
+      </c>
+      <c r="J19" s="21">
+        <v>3.36</v>
+      </c>
+      <c r="K19" s="32" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="35" t="s">
+      <c r="A20" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="37" t="s">
+      <c r="C20" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="D20" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="35">
-        <v>44.07</v>
-      </c>
-      <c r="G20" s="35">
-        <v>45.12</v>
-      </c>
-      <c r="H20" s="35">
-        <v>1.48</v>
-      </c>
-      <c r="I20" s="35">
-        <v>1.05</v>
+      <c r="E20" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="34">
+        <v>44.02</v>
+      </c>
+      <c r="G20" s="34">
+        <v>45.17</v>
+      </c>
+      <c r="H20" s="34">
+        <v>0.48</v>
+      </c>
+      <c r="I20" s="34">
+        <v>1.15</v>
       </c>
       <c r="J20" s="21">
-        <v>0.71</v>
-      </c>
-      <c r="K20" s="36" t="s">
+        <v>2.38</v>
+      </c>
+      <c r="K20" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="A23" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1687,31 +1677,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1734,13 +1724,13 @@
         <v>7.53</v>
       </c>
       <c r="G2" s="5">
-        <v>1.33</v>
+        <v>0.33</v>
       </c>
       <c r="H2" s="5">
         <v>7.53</v>
       </c>
       <c r="I2" s="8">
-        <v>5.65</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1789,16 +1779,16 @@
         <v>9.42</v>
       </c>
       <c r="F4" s="12">
-        <v>18.42</v>
+        <v>17.42</v>
       </c>
       <c r="G4" s="12">
         <v>0.83</v>
       </c>
       <c r="H4" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I4" s="8">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1809,25 +1799,25 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>18.42</v>
+        <v>17.42</v>
       </c>
       <c r="F5" s="15">
-        <v>24.32</v>
+        <v>21.32</v>
       </c>
       <c r="G5" s="15">
         <v>0.57</v>
       </c>
       <c r="H5" s="15">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="I5" s="8">
-        <v>10.41</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1838,25 +1828,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>24.32</v>
+        <v>21.32</v>
       </c>
       <c r="F6" s="18">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="G6" s="18">
         <v>0.9</v>
       </c>
       <c r="H6" s="18">
-        <v>0.78</v>
+        <v>4.08</v>
       </c>
       <c r="I6" s="21">
-        <v>0.87</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1867,13 +1857,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="F7" s="22">
         <v>35.8</v>
@@ -1882,10 +1872,10 @@
         <v>0.67</v>
       </c>
       <c r="H7" s="22">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="I7" s="8">
-        <v>16.05</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1896,7 +1886,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1905,132 +1895,132 @@
         <v>35.8</v>
       </c>
       <c r="F8" s="25">
-        <v>38.34</v>
+        <v>37.84</v>
       </c>
       <c r="G8" s="25">
         <v>1.15</v>
       </c>
       <c r="H8" s="25">
-        <v>2.54</v>
-      </c>
-      <c r="I8" s="28">
-        <v>2.21</v>
+        <v>2.04</v>
+      </c>
+      <c r="I8" s="21">
+        <v>1.77</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="29">
+      <c r="C9" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
-        <v>38.34</v>
-      </c>
-      <c r="F9" s="29">
+      <c r="E9" s="28">
+        <v>37.84</v>
+      </c>
+      <c r="F9" s="28">
         <v>39.6</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>0.48</v>
       </c>
-      <c r="H9" s="29">
-        <v>1.26</v>
-      </c>
-      <c r="I9" s="28">
-        <v>2.61</v>
+      <c r="H9" s="28">
+        <v>1.76</v>
+      </c>
+      <c r="I9" s="21">
+        <v>3.64</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="31">
         <v>9</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="32">
+      <c r="C10" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="31">
         <v>1</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="31">
         <v>39.6</v>
       </c>
-      <c r="F10" s="32">
-        <v>44.07</v>
-      </c>
-      <c r="G10" s="32">
+      <c r="F10" s="31">
+        <v>44.02</v>
+      </c>
+      <c r="G10" s="31">
         <v>1.32</v>
       </c>
-      <c r="H10" s="32">
-        <v>4.47</v>
-      </c>
-      <c r="I10" s="28">
-        <v>3.39</v>
+      <c r="H10" s="31">
+        <v>4.42</v>
+      </c>
+      <c r="I10" s="21">
+        <v>3.36</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="35">
+      <c r="C11" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="34">
         <v>1</v>
       </c>
-      <c r="E11" s="35">
-        <v>44.07</v>
-      </c>
-      <c r="F11" s="35">
-        <v>45.12</v>
-      </c>
-      <c r="G11" s="35">
-        <v>1.48</v>
-      </c>
-      <c r="H11" s="35">
-        <v>1.05</v>
+      <c r="E11" s="34">
+        <v>44.02</v>
+      </c>
+      <c r="F11" s="34">
+        <v>45.17</v>
+      </c>
+      <c r="G11" s="34">
+        <v>0.48</v>
+      </c>
+      <c r="H11" s="34">
+        <v>1.15</v>
       </c>
       <c r="I11" s="21">
-        <v>0.71</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="40" t="s">
+      <c r="A12" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="39">
         <v>0</v>
       </c>
-      <c r="F12" s="40">
-        <v>45.12</v>
-      </c>
-      <c r="G12" s="40">
-        <v>9.05</v>
-      </c>
-      <c r="H12" s="40">
-        <v>45.12</v>
-      </c>
-      <c r="I12" s="40">
-        <v>4.99</v>
+      <c r="F12" s="39">
+        <v>45.17</v>
+      </c>
+      <c r="G12" s="39">
+        <v>7.05</v>
+      </c>
+      <c r="H12" s="39">
+        <v>45.17</v>
+      </c>
+      <c r="I12" s="39">
+        <v>6.41</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/607e0e0c-05b6-4e68-a67b-e50624c0c032_LÔ_CT-02_P7-132_D800_18-03-2026.xlsx
+++ b/SGC-CKN/Excel/607e0e0c-05b6-4e68-a67b-e50624c0c032_LÔ_CT-02_P7-132_D800_18-03-2026.xlsx
@@ -207,7 +207,7 @@
 18/03/2026</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>16.2.Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15:21
